--- a/artfynd/A 53716-2025 artfynd.xlsx
+++ b/artfynd/A 53716-2025 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136151583</v>
       </c>
       <c r="B5" t="n">
-        <v>106654</v>
+        <v>106657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>136151584</v>
       </c>
       <c r="B6" t="n">
-        <v>106654</v>
+        <v>106657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53716-2025 artfynd.xlsx
+++ b/artfynd/A 53716-2025 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136151583</v>
       </c>
       <c r="B5" t="n">
-        <v>106657</v>
+        <v>106658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>136151584</v>
       </c>
       <c r="B6" t="n">
-        <v>106657</v>
+        <v>106658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53716-2025 artfynd.xlsx
+++ b/artfynd/A 53716-2025 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>136151583</v>
       </c>
       <c r="B5" t="n">
-        <v>106658</v>
+        <v>106663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>136151584</v>
       </c>
       <c r="B6" t="n">
-        <v>106658</v>
+        <v>106663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
